--- a/gpu-training-memory-sizing.xlsx
+++ b/gpu-training-memory-sizing.xlsx
@@ -739,6 +739,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="19.5" customHeight="1" s="38">
       <c r="A5" s="42" t="inlineStr">
         <is>
@@ -763,6 +764,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="23.85" customHeight="1" s="38">
       <c r="A8" s="43" t="inlineStr">
         <is>
@@ -903,6 +905,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="19.5" customHeight="1" s="38">
       <c r="A17" s="42" t="inlineStr">
         <is>
@@ -1015,6 +1018,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="19.5" customHeight="1" s="38">
       <c r="A26" s="42" t="inlineStr">
         <is>
@@ -1074,6 +1078,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="19.5" customHeight="1" s="38">
       <c r="A32" s="42" t="inlineStr">
         <is>
@@ -1107,7 +1112,7 @@
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
-          <t>Measured range 0.95-1.11 GB across two configurations in runs/20260731-1200/results.csv. Source: benchmark/predictions.py, FRAGMENTATION_GB.</t>
+          <t>Measured range 0.95-1.11 GB across two configurations in benchmark/reference-run/results.csv. Source: benchmark/predictions.py, FRAGMENTATION_GB.</t>
         </is>
       </c>
     </row>
@@ -1122,10 +1127,11 @@
       </c>
       <c r="C35" s="45" t="inlineStr">
         <is>
-          <t>Measured range 3.58-6.12 GB across three configurations in runs/20260731-1200/results.csv. Provisional. Source: benchmark/predictions.py, CHECKPOINTING_FRAGMENTATION_GB.</t>
-        </is>
-      </c>
-    </row>
+          <t>Measured range 3.58-6.12 GB across three configurations in benchmark/reference-run/results.csv. Provisional. Source: benchmark/predictions.py, CHECKPOINTING_FRAGMENTATION_GB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37" ht="19.5" customHeight="1" s="38">
       <c r="A37" s="42" t="inlineStr">
         <is>
@@ -1241,6 +1247,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46" ht="19.5" customHeight="1" s="38">
       <c r="A46" s="42" t="inlineStr">
         <is>
@@ -1345,6 +1352,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55" ht="19.5" customHeight="1" s="38">
       <c r="A55" s="42" t="inlineStr">
         <is>
@@ -1386,6 +1394,7 @@
         <v/>
       </c>
     </row>
+    <row r="59"/>
     <row r="60" ht="19.5" customHeight="1" s="38">
       <c r="A60" s="42" t="inlineStr">
         <is>
@@ -1544,10 +1553,11 @@
         <v/>
       </c>
     </row>
+    <row r="72"/>
     <row r="73" ht="15" customHeight="1" s="38">
       <c r="A73" s="64" t="inlineStr">
         <is>
-          <t>Source for every formula on this tab: benchmark/predictions.py in odog96/gpu-sizing-playbook, validated against the 24-configuration H100 80GB sweep in runs/20260731-1200/results.csv. See the Validation tab for the config-by-config comparison, and the Notes &amp; Sources tab for what is measured, calculated, and unvalidated.</t>
+          <t>Source for every formula on this tab: benchmark/predictions.py in odog96/gpu-sizing-playbook, validated against the 24-configuration H100 80GB sweep in benchmark/reference-run/results.csv. See the Validation tab for the config-by-config comparison, and the Notes &amp; Sources tab for what is measured, calculated, and unvalidated.</t>
         </is>
       </c>
     </row>
@@ -1562,9 +1572,9 @@
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="B56:C56"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
@@ -1628,6 +1638,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="38">
       <c r="A4" s="67" t="inlineStr">
         <is>
@@ -1697,7 +1708,7 @@
       </c>
       <c r="H5" s="68" t="inlineStr">
         <is>
-          <t>Exact architecture benchmarked in runs/20260731-1200/results.csv</t>
+          <t>Exact architecture benchmarked in benchmark/reference-run/results.csv</t>
         </is>
       </c>
     </row>
@@ -1949,6 +1960,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="38">
       <c r="A15" s="64" t="inlineStr">
         <is>
@@ -1997,6 +2009,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="38">
       <c r="A4" s="67" t="inlineStr">
         <is>
@@ -2278,7 +2291,7 @@
     <row r="2" ht="15" customHeight="1" s="38">
       <c r="A2" s="66" t="inlineStr">
         <is>
-          <t>Every white column is calculated live by the same arithmetic as the Sizing Tool tab. The measured columns come from runs/20260731-1200/results.csv in odog96/gpu-sizing-playbook. Error is calculated peak allocated against measured peak allocated; blank where the configuration ran out of memory.</t>
+          <t>Every white column is calculated live by the same arithmetic as the Sizing Tool tab. The measured columns come from benchmark/reference-run/results.csv in odog96/gpu-sizing-playbook. Error is calculated peak allocated against measured peak allocated; blank where the configuration ran out of memory.</t>
         </is>
       </c>
     </row>
@@ -2293,6 +2306,7 @@
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="45.75" customHeight="1" s="38">
       <c r="A5" s="67" t="inlineStr">
         <is>
@@ -5810,6 +5824,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="38">
       <c r="A31" s="43" t="inlineStr">
         <is>
@@ -5855,6 +5870,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="45.75" customHeight="1" s="38">
       <c r="A3" s="43" t="inlineStr">
         <is>
@@ -5887,7 +5903,7 @@
       </c>
       <c r="B5" s="75" t="inlineStr">
         <is>
-          <t>runs/20260731-1200/results.csv — a 24-configuration training sweep on a single NVIDIA H100 80GB, varying batch size, sequence length, optimizer, compute precision, and activation checkpointing.</t>
+          <t>benchmark/reference-run/results.csv — a 24-configuration training sweep on a single NVIDIA H100 80GB, varying batch size, sequence length, optimizer, compute precision, and activation checkpointing.</t>
         </is>
       </c>
     </row>
